--- a/data/trans_orig/RUIDO_2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_2-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los motivos por los que no pagaría para realizar actuaciones que reduzcan el ruido en su municipio o lugar de residencia en 2023</t>
+          <t>Población según los motivos por los que no pagaría para realizar actuaciones que reduzcan el ruido en su municipio o lugar de residencia en 2023 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12100</t>
+          <t>12461</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28492</t>
+          <t>30469</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18320</t>
+          <t>18941</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32283</t>
+          <t>33218</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35231</t>
+          <t>34116</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56471</t>
+          <t>55537</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75685</t>
+          <t>75527</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101063</t>
+          <t>101010</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>137415</t>
+          <t>137830</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>165723</t>
+          <t>164827</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>221734</t>
+          <t>222738</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>258822</t>
+          <t>257259</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,58%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45338</t>
+          <t>43417</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66392</t>
+          <t>65944</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53987</t>
+          <t>54162</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74823</t>
+          <t>74470</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>104178</t>
+          <t>103999</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>133838</t>
+          <t>134339</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,8%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18341</t>
+          <t>18788</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34836</t>
+          <t>35259</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39322</t>
+          <t>39313</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58854</t>
+          <t>58620</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62028</t>
+          <t>61729</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87325</t>
+          <t>87115</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26958</t>
+          <t>27757</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45942</t>
+          <t>47888</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41828</t>
+          <t>42820</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60707</t>
+          <t>61680</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>74391</t>
+          <t>74518</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101519</t>
+          <t>101445</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65237</t>
+          <t>63296</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>126059</t>
+          <t>120034</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36117</t>
+          <t>38011</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102714</t>
+          <t>101798</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>109424</t>
+          <t>109017</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>204140</t>
+          <t>202223</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>157628</t>
+          <t>156118</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>210512</t>
+          <t>212253</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>261130</t>
+          <t>262557</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>682150</t>
+          <t>663234</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>432640</t>
+          <t>428088</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1010363</t>
+          <t>972491</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>55,63%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>298445</t>
+          <t>299926</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>357556</t>
+          <t>359778</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>127896</t>
+          <t>136600</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>343532</t>
+          <t>341577</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>372697</t>
+          <t>398588</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>684630</t>
+          <t>684063</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,13%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>102814</t>
+          <t>102278</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>145940</t>
+          <t>145612</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49416</t>
+          <t>45637</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129826</t>
+          <t>126443</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>147024</t>
+          <t>146878</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>257215</t>
+          <t>260832</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70433</t>
+          <t>70182</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>108381</t>
+          <t>108774</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46218</t>
+          <t>46779</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127383</t>
+          <t>127190</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>115956</t>
+          <t>125966</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>213972</t>
+          <t>215296</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13190</t>
+          <t>14259</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33528</t>
+          <t>34287</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15162</t>
+          <t>15474</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32950</t>
+          <t>32111</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32125</t>
+          <t>33003</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60149</t>
+          <t>60270</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21728</t>
+          <t>21026</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17825</t>
+          <t>18201</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34464</t>
+          <t>33884</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27959</t>
+          <t>26235</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50669</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>88808</t>
+          <t>88341</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>123156</t>
+          <t>120702</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>92452</t>
+          <t>92144</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>117192</t>
+          <t>117807</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>190469</t>
+          <t>189739</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>230916</t>
+          <t>232470</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>54,26%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24532</t>
+          <t>25501</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48859</t>
+          <t>48042</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22870</t>
+          <t>23722</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40984</t>
+          <t>40345</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52368</t>
+          <t>52716</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81329</t>
+          <t>81559</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23428</t>
+          <t>22803</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44614</t>
+          <t>45259</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28111</t>
+          <t>28580</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48262</t>
+          <t>47424</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57048</t>
+          <t>56765</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87020</t>
+          <t>86378</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>102542</t>
+          <t>100118</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>162833</t>
+          <t>168573</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70971</t>
+          <t>77338</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>149200</t>
+          <t>149078</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>186198</t>
+          <t>190604</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>296591</t>
+          <t>295697</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>249557</t>
+          <t>251022</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>317762</t>
+          <t>318027</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>439286</t>
+          <t>441103</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>934020</t>
+          <t>940343</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>706051</t>
+          <t>706364</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1361953</t>
+          <t>1331181</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>48,57%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>449829</t>
+          <t>452778</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>527363</t>
+          <t>527848</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>268007</t>
+          <t>262333</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>506846</t>
+          <t>508567</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>682960</t>
+          <t>697745</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1012505</t>
+          <t>1009993</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>159210</t>
+          <t>161225</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>211699</t>
+          <t>211508</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>109872</t>
+          <t>104397</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>208300</t>
+          <t>208343</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>269968</t>
+          <t>266683</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>402699</t>
+          <t>405559</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>133795</t>
+          <t>133867</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>181298</t>
+          <t>183520</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>111342</t>
+          <t>103852</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>219741</t>
+          <t>219299</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>253869</t>
+          <t>258518</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>382563</t>
+          <t>379350</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_2-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19171</t>
+          <t>20415</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>12852</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30469</t>
+          <t>30603</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25271</t>
+          <t>27456</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18941</t>
+          <t>20469</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33218</t>
+          <t>35749</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>44441</t>
+          <t>47871</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34116</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55537</t>
+          <t>61395</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>88300</t>
+          <t>106504</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75527</t>
+          <t>92433</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101010</t>
+          <t>120829</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>151504</t>
+          <t>164615</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>137830</t>
+          <t>149872</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>164827</t>
+          <t>179041</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>239804</t>
+          <t>271119</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>222738</t>
+          <t>249645</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>257259</t>
+          <t>290492</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>46,08%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>54718</t>
+          <t>61080</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43417</t>
+          <t>48903</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65944</t>
+          <t>73514</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63762</t>
+          <t>69870</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54162</t>
+          <t>58534</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74470</t>
+          <t>81275</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118480</t>
+          <t>130951</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>103999</t>
+          <t>114927</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>134339</t>
+          <t>149030</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26276</t>
+          <t>29482</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18788</t>
+          <t>21614</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35259</t>
+          <t>42391</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47762</t>
+          <t>54362</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39313</t>
+          <t>44344</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58620</t>
+          <t>65222</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>74039</t>
+          <t>83843</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61729</t>
+          <t>70765</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87115</t>
+          <t>99105</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>36478</t>
+          <t>39970</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27757</t>
+          <t>30466</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47888</t>
+          <t>51548</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>51164</t>
+          <t>56684</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42820</t>
+          <t>46570</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61680</t>
+          <t>67461</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,22 +1247,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>87642</t>
+          <t>96654</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>74518</t>
+          <t>83222</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101445</t>
+          <t>112803</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>224943</t>
+          <t>257451</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>224943</t>
+          <t>257451</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>224943</t>
+          <t>257451</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>339463</t>
+          <t>372987</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>339463</t>
+          <t>372987</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>339463</t>
+          <t>372987</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>564406</t>
+          <t>630438</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>564406</t>
+          <t>630438</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>564406</t>
+          <t>630438</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>87316</t>
+          <t>84517</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63296</t>
+          <t>62791</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120034</t>
+          <t>114221</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>73552</t>
+          <t>83110</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38011</t>
+          <t>67261</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>101798</t>
+          <t>101378</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>160867</t>
+          <t>167626</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>109017</t>
+          <t>141309</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>202223</t>
+          <t>204986</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>182349</t>
+          <t>211390</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>156118</t>
+          <t>183441</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>212253</t>
+          <t>242224</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>415962</t>
+          <t>243034</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>262557</t>
+          <t>219650</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>663234</t>
+          <t>268741</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>598311</t>
+          <t>454424</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>428088</t>
+          <t>418065</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>972491</t>
+          <t>491979</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>329274</t>
+          <t>350758</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>299926</t>
+          <t>317208</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>359778</t>
+          <t>383337</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>260818</t>
+          <t>279277</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>136600</t>
+          <t>256726</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>341577</t>
+          <t>306241</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>590092</t>
+          <t>630034</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>398588</t>
+          <t>590574</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>684063</t>
+          <t>673684</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,68%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>123225</t>
+          <t>137925</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>102278</t>
+          <t>115283</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>145612</t>
+          <t>163639</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>94803</t>
+          <t>103627</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45637</t>
+          <t>87243</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126443</t>
+          <t>121438</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>218028</t>
+          <t>241552</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>146878</t>
+          <t>211087</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>260832</t>
+          <t>271262</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>86748</t>
+          <t>96299</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70182</t>
+          <t>76047</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>108774</t>
+          <t>116178</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>94013</t>
+          <t>107891</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46779</t>
+          <t>90528</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127190</t>
+          <t>126390</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>180761</t>
+          <t>204190</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>125966</t>
+          <t>178598</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>215296</t>
+          <t>231292</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>808911</t>
+          <t>880888</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>808911</t>
+          <t>880888</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>808911</t>
+          <t>880888</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>939148</t>
+          <t>816938</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>939148</t>
+          <t>816938</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>939148</t>
+          <t>816938</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1748059</t>
+          <t>1697826</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1748059</t>
+          <t>1697826</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1748059</t>
+          <t>1697826</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>21968</t>
+          <t>23284</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14259</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34287</t>
+          <t>35474</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>22719</t>
+          <t>25955</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15474</t>
+          <t>18056</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32111</t>
+          <t>37270</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>44687</t>
+          <t>49238</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33003</t>
+          <t>36858</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60270</t>
+          <t>67017</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12694</t>
+          <t>15254</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>8326</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21026</t>
+          <t>26274</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>24950</t>
+          <t>35524</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18201</t>
+          <t>26143</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33884</t>
+          <t>47090</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>37644</t>
+          <t>50778</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26235</t>
+          <t>38162</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>64714</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>104384</t>
+          <t>106085</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>88341</t>
+          <t>91682</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>120702</t>
+          <t>124402</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>105824</t>
+          <t>115484</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>92144</t>
+          <t>100590</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>117807</t>
+          <t>129240</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>210209</t>
+          <t>221569</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>189739</t>
+          <t>199328</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>232470</t>
+          <t>243067</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>51,87%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34928</t>
+          <t>35938</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25501</t>
+          <t>25810</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48042</t>
+          <t>48003</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31011</t>
+          <t>33079</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23722</t>
+          <t>24359</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40345</t>
+          <t>42748</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>65939</t>
+          <t>69016</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52716</t>
+          <t>55484</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81559</t>
+          <t>84650</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32956</t>
+          <t>36214</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22803</t>
+          <t>26807</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45259</t>
+          <t>48787</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,27 +2576,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>36979</t>
+          <t>41825</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28580</t>
+          <t>32531</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47424</t>
+          <t>53926</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>69935</t>
+          <t>78039</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>56765</t>
+          <t>64627</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86378</t>
+          <t>96003</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>206930</t>
+          <t>216774</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>206930</t>
+          <t>216774</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>206930</t>
+          <t>216774</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>221482</t>
+          <t>251866</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>221482</t>
+          <t>251866</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>221482</t>
+          <t>251866</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>428413</t>
+          <t>468640</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>428413</t>
+          <t>468640</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>428413</t>
+          <t>468640</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>128454</t>
+          <t>128215</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>100118</t>
+          <t>100545</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>168573</t>
+          <t>157415</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>121542</t>
+          <t>136520</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>77338</t>
+          <t>115764</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>149078</t>
+          <t>159055</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>249995</t>
+          <t>264735</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>190604</t>
+          <t>229545</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>295697</t>
+          <t>303146</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>283343</t>
+          <t>333148</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>251022</t>
+          <t>299300</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>318027</t>
+          <t>370449</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>592416</t>
+          <t>443173</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>441103</t>
+          <t>411548</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>940343</t>
+          <t>471944</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>875759</t>
+          <t>776321</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>706364</t>
+          <t>732055</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1331181</t>
+          <t>821360</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>488377</t>
+          <t>517923</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>452778</t>
+          <t>479053</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>527848</t>
+          <t>557231</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>430405</t>
+          <t>464631</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>262333</t>
+          <t>434220</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>508567</t>
+          <t>495064</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>918781</t>
+          <t>982554</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>697745</t>
+          <t>929199</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1009993</t>
+          <t>1030517</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,84%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>184430</t>
+          <t>203344</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>161225</t>
+          <t>174729</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>211508</t>
+          <t>228736</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>173576</t>
+          <t>191067</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>104397</t>
+          <t>170472</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>208343</t>
+          <t>213802</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>358005</t>
+          <t>394411</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>266683</t>
+          <t>362605</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>405559</t>
+          <t>434613</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>156181</t>
+          <t>172483</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>133867</t>
+          <t>148996</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>183520</t>
+          <t>199318</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>182156</t>
+          <t>206400</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>103852</t>
+          <t>181129</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>219299</t>
+          <t>229589</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>338337</t>
+          <t>378883</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>258518</t>
+          <t>344705</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>379350</t>
+          <t>414770</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1240784</t>
+          <t>1355113</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1240784</t>
+          <t>1355113</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1240784</t>
+          <t>1355113</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1500094</t>
+          <t>1441791</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1500094</t>
+          <t>1441791</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1500094</t>
+          <t>1441791</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2740878</t>
+          <t>2796904</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2740878</t>
+          <t>2796904</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2740878</t>
+          <t>2796904</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
